--- a/web/test/24_单目标优化_参数范围.xlsx
+++ b/web/test/24_单目标优化_参数范围.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_Project\vue\DY_TS_L\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\DY2024_Public\web\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E67636A-D9B7-4287-AC94-4940731173B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06893A0F-B1CA-48AE-888E-A56614C96C39}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-105" windowWidth="25815" windowHeight="15615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,24 +27,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>Pipe_m</t>
-  </si>
-  <si>
     <t>Pipe_d</t>
   </si>
   <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>V-dep</t>
-  </si>
-  <si>
-    <t>angle-H</t>
-  </si>
-  <si>
-    <t>line_d</t>
-  </si>
-  <si>
     <t>cut-dep1</t>
   </si>
   <si>
@@ -58,6 +43,21 @@
   </si>
   <si>
     <t>cut-dep5</t>
+  </si>
+  <si>
+    <t>Pipe_a</t>
+  </si>
+  <si>
+    <t>Pipe_b</t>
+  </si>
+  <si>
+    <t>Pipe_c</t>
+  </si>
+  <si>
+    <t>Pipe_e</t>
+  </si>
+  <si>
+    <t>Pipe_f</t>
   </si>
 </sst>
 </file>
@@ -393,37 +393,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
